--- a/107班分组名单(最新）(1)-3(2).xlsx
+++ b/107班分组名单(最新）(1)-3(2).xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\UserComputer\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\infomation-of-107\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -40,7 +40,7 @@
     <t>组号</t>
   </si>
   <si>
-    <t xml:space="preserve"> 组长</t>
+    <t>组长</t>
   </si>
   <si>
     <t>组员共计</t>
@@ -472,7 +472,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -487,127 +487,121 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -906,7 +900,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -930,16 +924,16 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -948,89 +942,89 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1067,9 +1061,6 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1079,23 +1070,14 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -1717,13 +1699,13 @@
       <c r="C3" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="E3" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="12" t="s">
+      <c r="F3" s="11" t="s">
         <v>9</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -1732,7 +1714,7 @@
       <c r="H3" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="I3" s="12" t="s">
+      <c r="I3" s="11" t="s">
         <v>12</v>
       </c>
       <c r="J3" s="11" t="s">
@@ -1741,7 +1723,7 @@
       <c r="K3" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="L3" s="12" t="s">
+      <c r="L3" s="11" t="s">
         <v>15</v>
       </c>
       <c r="M3" s="11" t="s">
@@ -1750,10 +1732,10 @@
       <c r="N3" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="O3" s="13" t="s">
+      <c r="O3" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="P3" s="14" t="s">
+      <c r="P3" s="13" t="s">
         <v>19</v>
       </c>
     </row>
@@ -1764,46 +1746,46 @@
       <c r="B4" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="C4" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="D4" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="E4" s="15" t="s">
+      <c r="E4" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="F4" s="16" t="s">
+      <c r="F4" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="G4" s="16" t="s">
+      <c r="G4" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="H4" s="16" t="s">
+      <c r="H4" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="I4" s="17" t="s">
+      <c r="I4" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="J4" s="16" t="s">
+      <c r="J4" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="K4" s="16" t="s">
+      <c r="K4" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="L4" s="16" t="s">
+      <c r="L4" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="M4" s="16" t="s">
+      <c r="M4" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="N4" s="16" t="s">
+      <c r="N4" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="O4" s="18" t="s">
+      <c r="O4" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="P4" s="19" t="s">
+      <c r="P4" s="16" t="s">
         <v>19</v>
       </c>
     </row>
@@ -1814,43 +1796,43 @@
       <c r="B5" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="D5" s="16" t="s">
+      <c r="D5" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="E5" s="16" t="s">
+      <c r="E5" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="F5" s="16" t="s">
+      <c r="F5" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="G5" s="16" t="s">
+      <c r="G5" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="H5" s="16" t="s">
+      <c r="H5" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="I5" s="16" t="s">
+      <c r="I5" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="J5" s="16" t="s">
+      <c r="J5" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="K5" s="16" t="s">
+      <c r="K5" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="L5" s="15" t="s">
+      <c r="L5" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="M5" s="15" t="s">
+      <c r="M5" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="N5" s="16" t="s">
+      <c r="N5" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="O5" s="20" t="s">
+      <c r="O5" s="17" t="s">
         <v>45</v>
       </c>
       <c r="P5" s="9" t="s">
@@ -1864,43 +1846,43 @@
       <c r="B6" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="C6" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="D6" s="16" t="s">
+      <c r="D6" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="E6" s="15" t="s">
+      <c r="E6" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="F6" s="15" t="s">
+      <c r="F6" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="G6" s="16" t="s">
+      <c r="G6" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="H6" s="15" t="s">
+      <c r="H6" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="I6" s="15" t="s">
+      <c r="I6" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="J6" s="16" t="s">
+      <c r="J6" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="K6" s="16" t="s">
+      <c r="K6" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="L6" s="16" t="s">
+      <c r="L6" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="M6" s="15" t="s">
+      <c r="M6" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="N6" s="15" t="s">
+      <c r="N6" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="O6" s="20" t="s">
+      <c r="O6" s="17" t="s">
         <v>58</v>
       </c>
       <c r="P6" s="9" t="s">
@@ -1914,43 +1896,43 @@
       <c r="B7" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="C7" s="16" t="s">
+      <c r="C7" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="D7" s="15" t="s">
+      <c r="D7" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="E7" s="15" t="s">
+      <c r="E7" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="F7" s="16" t="s">
+      <c r="F7" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="G7" s="15" t="s">
+      <c r="G7" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="H7" s="16" t="s">
+      <c r="H7" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="I7" s="16" t="s">
+      <c r="I7" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="J7" s="15" t="s">
+      <c r="J7" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="K7" s="16" t="s">
+      <c r="K7" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="L7" s="16" t="s">
+      <c r="L7" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="M7" s="16" t="s">
+      <c r="M7" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="N7" s="16" t="s">
+      <c r="N7" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="O7" s="21"/>
+      <c r="O7" s="18"/>
       <c r="P7" s="9" t="s">
         <v>71</v>
       </c>
@@ -1962,43 +1944,43 @@
       <c r="B8" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="C8" s="16" t="s">
+      <c r="C8" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="D8" s="15" t="s">
+      <c r="D8" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="E8" s="16" t="s">
+      <c r="E8" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="F8" s="15" t="s">
+      <c r="F8" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="G8" s="16" t="s">
+      <c r="G8" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="H8" s="16" t="s">
+      <c r="H8" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="I8" s="16" t="s">
+      <c r="I8" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="J8" s="15" t="s">
+      <c r="J8" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="K8" s="15" t="s">
+      <c r="K8" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="L8" s="15" t="s">
+      <c r="L8" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="M8" s="15" t="s">
+      <c r="M8" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="N8" s="15" t="s">
+      <c r="N8" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="O8" s="22" t="s">
+      <c r="O8" s="18" t="s">
         <v>84</v>
       </c>
       <c r="P8" s="9" t="s">
@@ -2006,22 +1988,22 @@
       </c>
     </row>
     <row r="9" ht="15" spans="1:18">
-      <c r="A9" s="23"/>
-      <c r="B9" s="23"/>
-      <c r="C9" s="23"/>
-      <c r="D9" s="23"/>
-      <c r="E9" s="23"/>
-      <c r="F9" s="23"/>
-      <c r="G9" s="23"/>
-      <c r="H9" s="23"/>
-      <c r="I9" s="23"/>
-      <c r="J9" s="23"/>
-      <c r="K9" s="23"/>
-      <c r="L9" s="23"/>
-      <c r="M9" s="23"/>
-      <c r="N9" s="23"/>
-      <c r="O9" s="23"/>
-      <c r="P9" s="23"/>
+      <c r="A9" s="19"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="19"/>
+      <c r="H9" s="19"/>
+      <c r="I9" s="19"/>
+      <c r="J9" s="19"/>
+      <c r="K9" s="19"/>
+      <c r="L9" s="19"/>
+      <c r="M9" s="19"/>
+      <c r="N9" s="19"/>
+      <c r="O9" s="19"/>
+      <c r="P9" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="1">
